--- a/artfynd/A 3501-2025 artfynd.xlsx
+++ b/artfynd/A 3501-2025 artfynd.xlsx
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125699624</v>
+        <v>125699654</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,38 +995,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788168</v>
+        <v>788180</v>
       </c>
       <c r="R5" t="n">
-        <v>7370105</v>
+        <v>7370081</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1059,11 +1055,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Avbarkad klen gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,7 +1081,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125699654</v>
+        <v>125699655</v>
       </c>
       <c r="B6" t="n">
         <v>78967</v>
@@ -1125,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>788180</v>
+        <v>788276</v>
       </c>
       <c r="R6" t="n">
-        <v>7370081</v>
+        <v>7370070</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1187,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125699655</v>
+        <v>125699624</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1198,34 +1189,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788276</v>
+        <v>788168</v>
       </c>
       <c r="R7" t="n">
-        <v>7370070</v>
+        <v>7370105</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1258,6 +1253,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Avbarkad klen gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1284,7 +1284,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125699632</v>
+        <v>125699630</v>
       </c>
       <c r="B8" t="n">
         <v>57648</v>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>788325</v>
+        <v>788364</v>
       </c>
       <c r="R8" t="n">
-        <v>7370007</v>
+        <v>7369916</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1355,6 +1355,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Stort hål i torrtall, ca 15 cm.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,7 +1386,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125699630</v>
+        <v>125699632</v>
       </c>
       <c r="B9" t="n">
         <v>57648</v>
@@ -1416,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>788364</v>
+        <v>788325</v>
       </c>
       <c r="R9" t="n">
-        <v>7369916</v>
+        <v>7370007</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1452,11 +1457,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Stort hål i torrtall, ca 15 cm.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,53 +1483,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125699629</v>
+        <v>125699637</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>97215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788389</v>
+        <v>788275</v>
       </c>
       <c r="R10" t="n">
-        <v>7369941</v>
+        <v>7370050</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1562,11 +1554,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Bohål i tall. Ca 6-7 cm stort, 2,5 m från marken.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,45 +1580,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125699637</v>
+        <v>125699629</v>
       </c>
       <c r="B11" t="n">
-        <v>97208</v>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>788275</v>
+        <v>788389</v>
       </c>
       <c r="R11" t="n">
-        <v>7370050</v>
+        <v>7369941</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1664,6 +1659,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Bohål i tall. Ca 6-7 cm stort, 2,5 m från marken.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,7 +1693,7 @@
         <v>125699619</v>
       </c>
       <c r="B12" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>125699648</v>
       </c>
       <c r="B16" t="n">
-        <v>91216</v>
+        <v>91223</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>125699638</v>
       </c>
       <c r="B20" t="n">
-        <v>97208</v>
+        <v>97215</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 3501-2025 artfynd.xlsx
+++ b/artfynd/A 3501-2025 artfynd.xlsx
@@ -1787,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125699662</v>
+        <v>125699621</v>
       </c>
       <c r="B13" t="n">
-        <v>82779</v>
+        <v>57651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1798,34 +1798,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>788358</v>
+        <v>788223</v>
       </c>
       <c r="R13" t="n">
-        <v>7369992</v>
+        <v>7370031</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1858,6 +1862,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,10 +1893,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125699621</v>
+        <v>125699662</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>82779</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1895,38 +1904,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>788223</v>
+        <v>788358</v>
       </c>
       <c r="R14" t="n">
-        <v>7370031</v>
+        <v>7369992</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1959,11 +1964,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Avbarkad gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 3501-2025 artfynd.xlsx
+++ b/artfynd/A 3501-2025 artfynd.xlsx
@@ -987,7 +987,7 @@
         <v>125699654</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>125699655</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1483,45 +1483,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125699637</v>
+        <v>125699629</v>
       </c>
       <c r="B10" t="n">
-        <v>97215</v>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788275</v>
+        <v>788389</v>
       </c>
       <c r="R10" t="n">
-        <v>7370050</v>
+        <v>7369941</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1554,6 +1562,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bohål i tall. Ca 6-7 cm stort, 2,5 m från marken.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1580,53 +1593,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125699629</v>
+        <v>125699637</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>97218</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>788389</v>
+        <v>788275</v>
       </c>
       <c r="R11" t="n">
-        <v>7369941</v>
+        <v>7370050</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1659,11 +1664,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Bohål i tall. Ca 6-7 cm stort, 2,5 m från marken.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,7 +1693,7 @@
         <v>125699619</v>
       </c>
       <c r="B12" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1787,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125699621</v>
+        <v>125699662</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>82780</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1798,38 +1798,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>788223</v>
+        <v>788358</v>
       </c>
       <c r="R13" t="n">
-        <v>7370031</v>
+        <v>7369992</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1862,11 +1858,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Avbarkad gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1893,10 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125699662</v>
+        <v>125699621</v>
       </c>
       <c r="B14" t="n">
-        <v>82779</v>
+        <v>57651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1904,34 +1895,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>788358</v>
+        <v>788223</v>
       </c>
       <c r="R14" t="n">
-        <v>7369992</v>
+        <v>7370031</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1964,6 +1959,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2087,10 +2087,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125699648</v>
+        <v>125699626</v>
       </c>
       <c r="B16" t="n">
-        <v>91223</v>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2098,34 +2098,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>788166</v>
+        <v>788337</v>
       </c>
       <c r="R16" t="n">
-        <v>7370090</v>
+        <v>7369933</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2158,6 +2162,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2184,10 +2193,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125699645</v>
+        <v>125699648</v>
       </c>
       <c r="B17" t="n">
-        <v>56834</v>
+        <v>91224</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2195,21 +2204,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2219,10 +2228,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>788204</v>
+        <v>788166</v>
       </c>
       <c r="R17" t="n">
-        <v>7370086</v>
+        <v>7370090</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2281,10 +2290,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125699626</v>
+        <v>125699645</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>56834</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2292,16 +2301,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2310,20 +2319,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>788337</v>
+        <v>788204</v>
       </c>
       <c r="R18" t="n">
-        <v>7369933</v>
+        <v>7370086</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2356,11 +2361,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2390,7 +2390,7 @@
         <v>125699660</v>
       </c>
       <c r="B19" t="n">
-        <v>82779</v>
+        <v>82780</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>125699638</v>
       </c>
       <c r="B20" t="n">
-        <v>97215</v>
+        <v>97218</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 3501-2025 artfynd.xlsx
+++ b/artfynd/A 3501-2025 artfynd.xlsx
@@ -2087,10 +2087,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125699626</v>
+        <v>125699648</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>91224</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2098,38 +2098,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>788337</v>
+        <v>788166</v>
       </c>
       <c r="R16" t="n">
-        <v>7369933</v>
+        <v>7370090</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2162,11 +2158,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2193,10 +2184,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125699648</v>
+        <v>125699645</v>
       </c>
       <c r="B17" t="n">
-        <v>91224</v>
+        <v>56834</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2204,21 +2195,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2228,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>788166</v>
+        <v>788204</v>
       </c>
       <c r="R17" t="n">
-        <v>7370090</v>
+        <v>7370086</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2290,10 +2281,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125699645</v>
+        <v>125699626</v>
       </c>
       <c r="B18" t="n">
-        <v>56834</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2301,16 +2292,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2319,16 +2310,20 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>788204</v>
+        <v>788337</v>
       </c>
       <c r="R18" t="n">
-        <v>7370086</v>
+        <v>7369933</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2361,6 +2356,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 3501-2025 artfynd.xlsx
+++ b/artfynd/A 3501-2025 artfynd.xlsx
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125699654</v>
+        <v>125699624</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,34 +995,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788180</v>
+        <v>788168</v>
       </c>
       <c r="R5" t="n">
-        <v>7370081</v>
+        <v>7370105</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1055,6 +1059,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Avbarkad klen gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,10 +1090,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125699655</v>
+        <v>125699654</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>788276</v>
+        <v>788180</v>
       </c>
       <c r="R6" t="n">
-        <v>7370070</v>
+        <v>7370081</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,10 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125699624</v>
+        <v>125699655</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,38 +1198,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788168</v>
+        <v>788276</v>
       </c>
       <c r="R7" t="n">
-        <v>7370105</v>
+        <v>7370070</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1253,11 +1258,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Avbarkad klen gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1483,53 +1483,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125699629</v>
+        <v>125699637</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>97222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788389</v>
+        <v>788275</v>
       </c>
       <c r="R10" t="n">
-        <v>7369941</v>
+        <v>7370050</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1562,11 +1554,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Bohål i tall. Ca 6-7 cm stort, 2,5 m från marken.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,45 +1580,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125699637</v>
+        <v>125699629</v>
       </c>
       <c r="B11" t="n">
-        <v>97218</v>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>788275</v>
+        <v>788389</v>
       </c>
       <c r="R11" t="n">
-        <v>7370050</v>
+        <v>7369941</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1664,6 +1659,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Bohål i tall. Ca 6-7 cm stort, 2,5 m från marken.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,7 +1693,7 @@
         <v>125699619</v>
       </c>
       <c r="B12" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>125699662</v>
       </c>
       <c r="B13" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>125699648</v>
       </c>
       <c r="B16" t="n">
-        <v>91224</v>
+        <v>91228</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,10 +2184,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125699645</v>
+        <v>125699626</v>
       </c>
       <c r="B17" t="n">
-        <v>56834</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2213,16 +2213,20 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>788204</v>
+        <v>788337</v>
       </c>
       <c r="R17" t="n">
-        <v>7370086</v>
+        <v>7369933</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2255,6 +2259,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2281,10 +2290,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125699626</v>
+        <v>125699645</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>56834</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2292,16 +2301,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2310,20 +2319,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>788337</v>
+        <v>788204</v>
       </c>
       <c r="R18" t="n">
-        <v>7369933</v>
+        <v>7370086</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2356,11 +2361,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2390,7 +2390,7 @@
         <v>125699660</v>
       </c>
       <c r="B19" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>125699638</v>
       </c>
       <c r="B20" t="n">
-        <v>97218</v>
+        <v>97222</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 3501-2025 artfynd.xlsx
+++ b/artfynd/A 3501-2025 artfynd.xlsx
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125699624</v>
+        <v>125699655</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,38 +995,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788168</v>
+        <v>788276</v>
       </c>
       <c r="R5" t="n">
-        <v>7370105</v>
+        <v>7370070</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1059,11 +1055,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Avbarkad klen gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1187,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125699655</v>
+        <v>125699624</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1198,34 +1189,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788276</v>
+        <v>788168</v>
       </c>
       <c r="R7" t="n">
-        <v>7370070</v>
+        <v>7370105</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1258,6 +1253,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Avbarkad klen gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1483,45 +1483,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125699637</v>
+        <v>125699629</v>
       </c>
       <c r="B10" t="n">
-        <v>97222</v>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788275</v>
+        <v>788389</v>
       </c>
       <c r="R10" t="n">
-        <v>7370050</v>
+        <v>7369941</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1554,6 +1562,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bohål i tall. Ca 6-7 cm stort, 2,5 m från marken.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1580,53 +1593,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125699629</v>
+        <v>125699637</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>97223</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>788389</v>
+        <v>788275</v>
       </c>
       <c r="R11" t="n">
-        <v>7369941</v>
+        <v>7370050</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1659,11 +1664,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Bohål i tall. Ca 6-7 cm stort, 2,5 m från marken.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2487,7 +2487,7 @@
         <v>125699638</v>
       </c>
       <c r="B20" t="n">
-        <v>97222</v>
+        <v>97223</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 3501-2025 artfynd.xlsx
+++ b/artfynd/A 3501-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125699622</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125699628</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>125699631</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125699655</v>
+        <v>125699654</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788276</v>
+        <v>788180</v>
       </c>
       <c r="R5" t="n">
-        <v>7370070</v>
+        <v>7370081</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1081,10 +1081,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125699654</v>
+        <v>125699655</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>788180</v>
+        <v>788276</v>
       </c>
       <c r="R6" t="n">
-        <v>7370081</v>
+        <v>7370070</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1181,7 +1181,7 @@
         <v>125699624</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>125699630</v>
       </c>
       <c r="B8" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>125699632</v>
       </c>
       <c r="B9" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>125699629</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>125699637</v>
       </c>
       <c r="B11" t="n">
-        <v>97223</v>
+        <v>97225</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>125699619</v>
       </c>
       <c r="B12" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>125699662</v>
       </c>
       <c r="B13" t="n">
-        <v>82784</v>
+        <v>82785</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>125699621</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>125699643</v>
       </c>
       <c r="B15" t="n">
-        <v>56834</v>
+        <v>56835</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>125699648</v>
       </c>
       <c r="B16" t="n">
-        <v>91228</v>
+        <v>91230</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,10 +2184,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125699626</v>
+        <v>125699645</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>56835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2213,20 +2213,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>788337</v>
+        <v>788204</v>
       </c>
       <c r="R17" t="n">
-        <v>7369933</v>
+        <v>7370086</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2259,11 +2255,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2290,10 +2281,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125699645</v>
+        <v>125699626</v>
       </c>
       <c r="B18" t="n">
-        <v>56834</v>
+        <v>57652</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2301,16 +2292,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2319,16 +2310,20 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>788204</v>
+        <v>788337</v>
       </c>
       <c r="R18" t="n">
-        <v>7370086</v>
+        <v>7369933</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2361,6 +2356,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2390,7 +2390,7 @@
         <v>125699660</v>
       </c>
       <c r="B19" t="n">
-        <v>82784</v>
+        <v>82785</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>125699638</v>
       </c>
       <c r="B20" t="n">
-        <v>97223</v>
+        <v>97225</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>125701258</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 3501-2025 artfynd.xlsx
+++ b/artfynd/A 3501-2025 artfynd.xlsx
@@ -2184,10 +2184,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125699645</v>
+        <v>125699626</v>
       </c>
       <c r="B17" t="n">
-        <v>56835</v>
+        <v>57652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2213,16 +2213,20 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>788204</v>
+        <v>788337</v>
       </c>
       <c r="R17" t="n">
-        <v>7370086</v>
+        <v>7369933</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2255,6 +2259,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2281,10 +2290,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125699626</v>
+        <v>125699645</v>
       </c>
       <c r="B18" t="n">
-        <v>57652</v>
+        <v>56835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2292,16 +2301,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2310,20 +2319,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>788337</v>
+        <v>788204</v>
       </c>
       <c r="R18" t="n">
-        <v>7369933</v>
+        <v>7370086</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2356,11 +2361,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 3501-2025 artfynd.xlsx
+++ b/artfynd/A 3501-2025 artfynd.xlsx
@@ -1596,7 +1596,7 @@
         <v>125699637</v>
       </c>
       <c r="B11" t="n">
-        <v>97225</v>
+        <v>97227</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>125699619</v>
       </c>
       <c r="B12" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1787,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125699662</v>
+        <v>125699621</v>
       </c>
       <c r="B13" t="n">
-        <v>82785</v>
+        <v>57652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1798,34 +1798,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>788358</v>
+        <v>788223</v>
       </c>
       <c r="R13" t="n">
-        <v>7369992</v>
+        <v>7370031</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1858,6 +1862,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,10 +1893,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125699621</v>
+        <v>125699662</v>
       </c>
       <c r="B14" t="n">
-        <v>57652</v>
+        <v>82785</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1895,38 +1904,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>788223</v>
+        <v>788358</v>
       </c>
       <c r="R14" t="n">
-        <v>7370031</v>
+        <v>7369992</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1959,11 +1964,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Avbarkad gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2087,10 +2087,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125699648</v>
+        <v>125699645</v>
       </c>
       <c r="B16" t="n">
-        <v>91230</v>
+        <v>56835</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2098,21 +2098,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>788166</v>
+        <v>788204</v>
       </c>
       <c r="R16" t="n">
-        <v>7370090</v>
+        <v>7370086</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2290,10 +2290,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125699645</v>
+        <v>125699648</v>
       </c>
       <c r="B18" t="n">
-        <v>56835</v>
+        <v>91232</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>788204</v>
+        <v>788166</v>
       </c>
       <c r="R18" t="n">
-        <v>7370086</v>
+        <v>7370090</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2487,7 +2487,7 @@
         <v>125699638</v>
       </c>
       <c r="B20" t="n">
-        <v>97225</v>
+        <v>97227</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 3501-2025 artfynd.xlsx
+++ b/artfynd/A 3501-2025 artfynd.xlsx
@@ -1483,53 +1483,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125699629</v>
+        <v>125699637</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>97227</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788389</v>
+        <v>788275</v>
       </c>
       <c r="R10" t="n">
-        <v>7369941</v>
+        <v>7370050</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1562,11 +1554,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Bohål i tall. Ca 6-7 cm stort, 2,5 m från marken.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,45 +1580,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125699637</v>
+        <v>125699629</v>
       </c>
       <c r="B11" t="n">
-        <v>97227</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>788275</v>
+        <v>788389</v>
       </c>
       <c r="R11" t="n">
-        <v>7370050</v>
+        <v>7369941</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1664,6 +1659,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Bohål i tall. Ca 6-7 cm stort, 2,5 m från marken.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 3501-2025 artfynd.xlsx
+++ b/artfynd/A 3501-2025 artfynd.xlsx
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125699654</v>
+        <v>125699624</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,34 +995,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788180</v>
+        <v>788168</v>
       </c>
       <c r="R5" t="n">
-        <v>7370081</v>
+        <v>7370105</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1055,6 +1059,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Avbarkad klen gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,7 +1090,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125699655</v>
+        <v>125699654</v>
       </c>
       <c r="B6" t="n">
         <v>78973</v>
@@ -1116,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>788276</v>
+        <v>788180</v>
       </c>
       <c r="R6" t="n">
-        <v>7370070</v>
+        <v>7370081</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,10 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125699624</v>
+        <v>125699655</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,38 +1198,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788168</v>
+        <v>788276</v>
       </c>
       <c r="R7" t="n">
-        <v>7370105</v>
+        <v>7370070</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1253,11 +1258,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Avbarkad klen gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1486,7 +1486,7 @@
         <v>125699637</v>
       </c>
       <c r="B10" t="n">
-        <v>97227</v>
+        <v>97229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>125699619</v>
       </c>
       <c r="B12" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2087,10 +2087,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125699645</v>
+        <v>125699626</v>
       </c>
       <c r="B16" t="n">
-        <v>56835</v>
+        <v>57652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2098,16 +2098,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2116,16 +2116,20 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>788204</v>
+        <v>788337</v>
       </c>
       <c r="R16" t="n">
-        <v>7370086</v>
+        <v>7369933</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2158,6 +2162,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2184,10 +2193,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125699626</v>
+        <v>125699645</v>
       </c>
       <c r="B17" t="n">
-        <v>57652</v>
+        <v>56835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2195,16 +2204,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2213,20 +2222,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>788337</v>
+        <v>788204</v>
       </c>
       <c r="R17" t="n">
-        <v>7369933</v>
+        <v>7370086</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2259,11 +2264,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2293,7 +2293,7 @@
         <v>125699648</v>
       </c>
       <c r="B18" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>125699638</v>
       </c>
       <c r="B20" t="n">
-        <v>97227</v>
+        <v>97229</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 3501-2025 artfynd.xlsx
+++ b/artfynd/A 3501-2025 artfynd.xlsx
@@ -1483,45 +1483,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125699637</v>
+        <v>125699629</v>
       </c>
       <c r="B10" t="n">
-        <v>97229</v>
+        <v>57652</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>788275</v>
+        <v>788389</v>
       </c>
       <c r="R10" t="n">
-        <v>7370050</v>
+        <v>7369941</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1554,6 +1562,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bohål i tall. Ca 6-7 cm stort, 2,5 m från marken.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1580,53 +1593,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125699629</v>
+        <v>125699637</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>97229</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>788389</v>
+        <v>788275</v>
       </c>
       <c r="R11" t="n">
-        <v>7369941</v>
+        <v>7370050</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1659,11 +1664,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Bohål i tall. Ca 6-7 cm stort, 2,5 m från marken.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1787,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125699621</v>
+        <v>125699662</v>
       </c>
       <c r="B13" t="n">
-        <v>57652</v>
+        <v>82785</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1798,38 +1798,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>788223</v>
+        <v>788358</v>
       </c>
       <c r="R13" t="n">
-        <v>7370031</v>
+        <v>7369992</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1862,11 +1858,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Avbarkad gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1893,10 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125699662</v>
+        <v>125699621</v>
       </c>
       <c r="B14" t="n">
-        <v>82785</v>
+        <v>57652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1904,34 +1895,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>788358</v>
+        <v>788223</v>
       </c>
       <c r="R14" t="n">
-        <v>7369992</v>
+        <v>7370031</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1964,6 +1959,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2087,10 +2087,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125699626</v>
+        <v>125699648</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>91234</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2098,38 +2098,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>788337</v>
+        <v>788166</v>
       </c>
       <c r="R16" t="n">
-        <v>7369933</v>
+        <v>7370090</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2162,11 +2158,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2193,10 +2184,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125699645</v>
+        <v>125699626</v>
       </c>
       <c r="B17" t="n">
-        <v>56835</v>
+        <v>57652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2204,16 +2195,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2222,16 +2213,20 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>788204</v>
+        <v>788337</v>
       </c>
       <c r="R17" t="n">
-        <v>7370086</v>
+        <v>7369933</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2264,6 +2259,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2290,10 +2290,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125699648</v>
+        <v>125699645</v>
       </c>
       <c r="B18" t="n">
-        <v>91234</v>
+        <v>56835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>788166</v>
+        <v>788204</v>
       </c>
       <c r="R18" t="n">
-        <v>7370090</v>
+        <v>7370086</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>

--- a/artfynd/A 3501-2025 artfynd.xlsx
+++ b/artfynd/A 3501-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125699622</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125699628</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>125699631</v>
       </c>
       <c r="B4" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125699624</v>
+        <v>125699654</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,38 +995,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788168</v>
+        <v>788180</v>
       </c>
       <c r="R5" t="n">
-        <v>7370105</v>
+        <v>7370081</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1059,11 +1055,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Avbarkad klen gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,10 +1081,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125699654</v>
+        <v>125699655</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>788180</v>
+        <v>788276</v>
       </c>
       <c r="R6" t="n">
-        <v>7370081</v>
+        <v>7370070</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1187,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125699655</v>
+        <v>125699624</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>57656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1198,34 +1189,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788276</v>
+        <v>788168</v>
       </c>
       <c r="R7" t="n">
-        <v>7370070</v>
+        <v>7370105</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1258,6 +1253,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Avbarkad klen gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,7 +1287,7 @@
         <v>125699630</v>
       </c>
       <c r="B8" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>125699632</v>
       </c>
       <c r="B9" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>125699629</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>125699637</v>
       </c>
       <c r="B11" t="n">
-        <v>97229</v>
+        <v>97233</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>125699619</v>
       </c>
       <c r="B12" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>125699662</v>
       </c>
       <c r="B13" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>125699621</v>
       </c>
       <c r="B14" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>125699643</v>
       </c>
       <c r="B15" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>125699648</v>
       </c>
       <c r="B16" t="n">
-        <v>91234</v>
+        <v>91238</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>125699626</v>
       </c>
       <c r="B17" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>125699645</v>
       </c>
       <c r="B18" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>125699660</v>
       </c>
       <c r="B19" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>125699638</v>
       </c>
       <c r="B20" t="n">
-        <v>97229</v>
+        <v>97233</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>125701258</v>
       </c>
       <c r="B21" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 3501-2025 artfynd.xlsx
+++ b/artfynd/A 3501-2025 artfynd.xlsx
@@ -984,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125699654</v>
+        <v>125699624</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,34 +995,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>788180</v>
+        <v>788168</v>
       </c>
       <c r="R5" t="n">
-        <v>7370081</v>
+        <v>7370105</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1055,6 +1059,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Avbarkad klen gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,7 +1090,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125699655</v>
+        <v>125699654</v>
       </c>
       <c r="B6" t="n">
         <v>78977</v>
@@ -1116,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>788276</v>
+        <v>788180</v>
       </c>
       <c r="R6" t="n">
-        <v>7370070</v>
+        <v>7370081</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,10 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125699624</v>
+        <v>125699655</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,38 +1198,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>788168</v>
+        <v>788276</v>
       </c>
       <c r="R7" t="n">
-        <v>7370105</v>
+        <v>7370070</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1253,11 +1258,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Avbarkad klen gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1596,7 +1596,7 @@
         <v>125699637</v>
       </c>
       <c r="B11" t="n">
-        <v>97233</v>
+        <v>97236</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2087,10 +2087,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125699648</v>
+        <v>125699645</v>
       </c>
       <c r="B16" t="n">
-        <v>91238</v>
+        <v>56839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2098,21 +2098,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>788166</v>
+        <v>788204</v>
       </c>
       <c r="R16" t="n">
-        <v>7370090</v>
+        <v>7370086</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2184,10 +2184,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125699626</v>
+        <v>125699648</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>91238</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2195,38 +2195,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>788337</v>
+        <v>788166</v>
       </c>
       <c r="R17" t="n">
-        <v>7369933</v>
+        <v>7370090</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2259,11 +2255,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2290,10 +2281,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125699645</v>
+        <v>125699626</v>
       </c>
       <c r="B18" t="n">
-        <v>56839</v>
+        <v>57656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2301,16 +2292,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2319,16 +2310,20 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Slätthedmyran, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>788204</v>
+        <v>788337</v>
       </c>
       <c r="R18" t="n">
-        <v>7370086</v>
+        <v>7369933</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2361,6 +2356,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,7 +2487,7 @@
         <v>125699638</v>
       </c>
       <c r="B20" t="n">
-        <v>97233</v>
+        <v>97236</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
